--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán Viejo</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:23</t>
+    <t xml:space="preserve">2026-10-04 08:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:54</t>
+    <t xml:space="preserve">2026-10-05 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -612,7 +612,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>947965.12</v>
+        <v>947965.13</v>
       </c>
     </row>
     <row r="7">
@@ -697,7 +697,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>894310.12</v>
+        <v>894310.13</v>
       </c>
     </row>
     <row r="12">
@@ -816,7 +816,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>826211.12</v>
+        <v>826211.13</v>
       </c>
     </row>
     <row r="19">
